--- a/data/Raw/ventas_marzo.xlsx
+++ b/data/Raw/ventas_marzo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\power\OneDrive\Escritorio\archivos_t\Proyectos\Proyecto Informe ventas\data\Raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B09559-4A1F-48C3-8E2A-C7A91D7576DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB57176-4ECA-46D9-B902-22FAB7CDD61E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="12">
   <si>
     <t>Fecha</t>
   </si>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="1"/>
@@ -496,7 +496,18 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
-      <c r="D6" s="2"/>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2750000</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
@@ -512,7 +523,7 @@
         <v>2750000</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -529,7 +540,7 @@
         <v>20000</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -546,6 +557,227 @@
         <v>74000</v>
       </c>
       <c r="E9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>45745</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2750000</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>45745</v>
+      </c>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2">
+        <v>20000</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>45745</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2750000</v>
+      </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>45745</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2">
+        <v>20000</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>45737</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2">
+        <v>74000</v>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>45745</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2750000</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>45745</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2">
+        <v>20000</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>45737</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2">
+        <v>74000</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>45745</v>
+      </c>
+      <c r="B18">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="2">
+        <v>20000</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>45737</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2">
+        <v>74000</v>
+      </c>
+      <c r="E19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>45745</v>
+      </c>
+      <c r="B20">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2">
+        <v>2750000</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>45745</v>
+      </c>
+      <c r="B21">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="2">
+        <v>20000</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>45737</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2">
+        <v>74000</v>
+      </c>
+      <c r="E22">
         <v>5</v>
       </c>
     </row>
